--- a/testcase/testcase.xlsx
+++ b/testcase/testcase.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8040" firstSheet="3" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8040" tabRatio="884"/>
   </bookViews>
   <sheets>
     <sheet name="ControlHeadLight" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="67">
   <si>
     <t>speedRxState</t>
   </si>
@@ -222,6 +222,22 @@
   </si>
   <si>
     <t>WARNING_NONE</t>
+  </si>
+  <si>
+    <t>testCaseId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testCaseId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testCaseId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testCaseId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -648,965 +664,1138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="18.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>"HL_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>HL_001</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5"/>
       <c r="C2" s="5"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="4"/>
+      <c r="J2" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A16" si="0">"HL_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>HL_002</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="4"/>
+      <c r="J3" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="4"/>
+      <c r="J4" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="4"/>
+      <c r="J5" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="4"/>
+      <c r="J6" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>10001</v>
       </c>
-      <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="7"/>
+      <c r="J7" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <v>10000</v>
       </c>
-      <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="7"/>
+      <c r="J8" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>9999</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="4">
         <v>1001</v>
       </c>
-      <c r="G9" s="4">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>9999</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="4">
         <v>1000</v>
       </c>
-      <c r="G10" s="4">
+      <c r="H10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="4"/>
+      <c r="J10" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="4">
         <v>9999</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="4">
         <v>999</v>
       </c>
-      <c r="G11" s="4">
+      <c r="H11" s="4">
         <v>0</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>1</v>
+      <c r="J11" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" s="4">
         <v>9999</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="4">
         <v>999</v>
       </c>
-      <c r="G12" s="4">
+      <c r="H12" s="4">
         <v>0</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>33</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>1</v>
+      <c r="J12" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <v>9999</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="4">
+      <c r="H13" s="4">
         <v>3001</v>
       </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="4"/>
+      <c r="J13" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_013</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>15</v>
-      </c>
       <c r="C14" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <v>9999</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="4">
         <v>0</v>
       </c>
-      <c r="G14" s="4">
+      <c r="H14" s="4">
         <v>3000</v>
       </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="4"/>
+      <c r="J14" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>1</v>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <v>9999</v>
       </c>
-      <c r="F15" s="4">
+      <c r="G15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="4">
+      <c r="H15" s="4">
         <v>2999</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>1</v>
+      <c r="J15" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f t="shared" si="0"/>
+        <v>HL_015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <v>9999</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="4">
         <v>0</v>
       </c>
-      <c r="G16" s="4">
+      <c r="H16" s="4">
         <v>2999</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="I16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="7" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>"WP_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>WP_001</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A25" si="0">"WP_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>WP_002</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_003</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="4"/>
+      <c r="H5" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_005</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="4"/>
+      <c r="H6" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_006</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="4"/>
       <c r="F7" s="4"/>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="4"/>
+      <c r="H7" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_007</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="E8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="4">
         <v>9</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="4">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="E9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="4">
         <v>10</v>
       </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="4">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="E10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="4">
         <v>11</v>
       </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="4">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4">
         <v>39</v>
       </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>1</v>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="E12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4">
         <v>40</v>
       </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="4">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>1</v>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="E13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="4">
         <v>41</v>
       </c>
-      <c r="F13" s="4">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>1</v>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="E14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="4">
         <v>69</v>
       </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>1</v>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="E15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="4">
         <v>70</v>
       </c>
-      <c r="F15" s="4">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="4">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>1</v>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="E16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="4">
         <v>71</v>
       </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="4">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>1</v>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="E17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="4">
         <v>9</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="H17" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>1</v>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_017</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="E18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="4">
         <v>10</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="H18" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>1</v>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_018</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="E19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="4">
         <v>11</v>
       </c>
-      <c r="F19" s="4">
+      <c r="G19" s="4">
         <v>0</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="H19" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>1</v>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_019</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="E20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4">
         <v>39</v>
       </c>
-      <c r="F20" s="4">
+      <c r="G20" s="4">
         <v>0</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="H20" s="7" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_020</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="E21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="4">
         <v>40</v>
       </c>
-      <c r="F21" s="4">
+      <c r="G21" s="4">
         <v>0</v>
       </c>
-      <c r="G21" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>1</v>
+      <c r="H21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_021</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="4">
+      <c r="E22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="4">
         <v>41</v>
       </c>
-      <c r="F22" s="4">
+      <c r="G22" s="4">
         <v>0</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>1</v>
+      <c r="H22" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_022</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="4">
+      <c r="E23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="4">
         <v>69</v>
       </c>
-      <c r="F23" s="4">
+      <c r="G23" s="4">
         <v>0</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>1</v>
+      <c r="H23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_023</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="4">
+      <c r="E24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="4">
         <v>70</v>
       </c>
-      <c r="F24" s="4">
+      <c r="G24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
+      <c r="H24" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" t="str">
+        <f t="shared" si="0"/>
+        <v>WP_024</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="4">
+      <c r="E25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="4">
         <v>71</v>
       </c>
-      <c r="F25" s="4">
+      <c r="G25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="7" t="s">
-        <v>46</v>
-      </c>
+      <c r="H25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1616,601 +1805,724 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>"DL_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>DL_001</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
-      <c r="E2" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="G2" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A31" si="0">"DL_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>DL_002</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
-      <c r="E3" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="E3" s="4"/>
       <c r="F3" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
+      <c r="G3" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_003</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E4" s="4"/>
       <c r="F4" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
+      <c r="G4" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_004</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>1</v>
+      <c r="G5" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_005</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>1</v>
+      <c r="G6" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_006</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>1</v>
+      <c r="G7" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_007</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>1</v>
+      <c r="G8" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_008</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>1</v>
+      <c r="G9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_009</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>1</v>
+      <c r="G10" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_010</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>1</v>
+      <c r="G11" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_011</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>1</v>
+      <c r="G12" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_012</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="E13" s="4"/>
       <c r="F13" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>1</v>
+      <c r="G13" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_013</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="4">
+      <c r="E14" s="4">
         <v>14</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F14" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>1</v>
+      <c r="G14" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_014</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="4">
+      <c r="E15" s="4">
         <v>14</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="F15" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>1</v>
+      <c r="G15" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_015</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="4">
-        <v>15</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>12</v>
+      <c r="E16" s="4">
+        <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>1</v>
+      <c r="G16" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_016</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="4">
-        <v>15</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>13</v>
+      <c r="E17" s="4">
+        <v>15</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_017</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="4">
+      <c r="E18" s="4">
         <v>16</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F18" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>1</v>
+      <c r="G18" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_018</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="4">
+      <c r="E19" s="4">
         <v>16</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="F19" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_019</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="4">
+      <c r="E20" s="4">
         <v>14</v>
       </c>
-      <c r="E20" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F20" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>1</v>
+      <c r="G20" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_020</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="4">
+      <c r="E21" s="4">
         <v>14</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="F21" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>1</v>
+      <c r="G21" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_021</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="4">
-        <v>15</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>12</v>
+      <c r="E22" s="4">
+        <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>1</v>
+      <c r="G22" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_022</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="4">
-        <v>15</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>13</v>
+      <c r="E23" s="4">
+        <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_023</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C24" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="4">
+      <c r="E24" s="4">
         <v>16</v>
       </c>
-      <c r="E24" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F24" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>1</v>
+      <c r="G24" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_024</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="4">
+      <c r="E25" s="4">
         <v>16</v>
       </c>
-      <c r="E25" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="F25" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_025</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="4">
+      <c r="E26" s="4">
         <v>14</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F26" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>1</v>
+      <c r="G26" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_026</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="4">
+      <c r="E27" s="4">
         <v>14</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="F27" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>1</v>
+      <c r="G27" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_027</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="4">
-        <v>15</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>12</v>
+      <c r="E28" s="4">
+        <v>15</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>1</v>
+      <c r="G28" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_028</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="4">
-        <v>15</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>13</v>
+      <c r="E29" s="4">
+        <v>15</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_029</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="4">
+      <c r="E30" s="4">
         <v>16</v>
       </c>
-      <c r="E30" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="F30" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>1</v>
+      <c r="G30" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="str">
+        <f t="shared" si="0"/>
+        <v>DL_030</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="4">
+      <c r="E31" s="4">
         <v>16</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="F31" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2222,49 +2534,58 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.5" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="12.75" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.375" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="13"/>
+    <col min="1" max="1" width="9" style="13"/>
+    <col min="2" max="2" width="6.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="12.75" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="14">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="str">
+        <f>"DOW_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>DOW_001</v>
+      </c>
+      <c r="B2" s="14">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="str">
+        <f t="shared" ref="A3:A18" si="0">"DOW_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>DOW_002</v>
+      </c>
+      <c r="B3" s="14">
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -2276,15 +2597,19 @@
         <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_003</v>
+      </c>
+      <c r="B4" s="14">
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
@@ -2293,121 +2618,145 @@
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
-        <v>1</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_004</v>
+      </c>
+      <c r="B5" s="14">
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_005</v>
+      </c>
+      <c r="B6" s="14">
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
-        <v>1</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_006</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
-        <v>1</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_007</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_008</v>
+      </c>
+      <c r="B9" s="14">
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_009</v>
+      </c>
+      <c r="B10" s="14">
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>13</v>
@@ -2416,18 +2765,22 @@
         <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
-        <v>1</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>13</v>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_010</v>
+      </c>
+      <c r="B11" s="14">
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>12</v>
@@ -2436,115 +2789,139 @@
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="14">
-        <v>1</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>13</v>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_011</v>
+      </c>
+      <c r="B12" s="14">
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
-        <v>1</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_012</v>
+      </c>
+      <c r="B13" s="14">
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
-        <v>1</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>13</v>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_013</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
-        <v>1</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>13</v>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_014</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="14">
-        <v>1</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>13</v>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_015</v>
+      </c>
+      <c r="B16" s="14">
+        <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="14">
-        <v>1</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>13</v>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_016</v>
+      </c>
+      <c r="B17" s="14">
+        <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>13</v>
@@ -2553,18 +2930,22 @@
         <v>13</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="14">
-        <v>1</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>13</v>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="str">
+        <f t="shared" si="0"/>
+        <v>DOW_017</v>
+      </c>
+      <c r="B18" s="14">
+        <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>13</v>
@@ -2576,128 +2957,131 @@
         <v>13</v>
       </c>
       <c r="F18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="14"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="14"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="14"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="14"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="14"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="14"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="14"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="14"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="14"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="14"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="14"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2707,66 +3091,93 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>"LSF_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>LSF_001</v>
+      </c>
+      <c r="B2" s="4">
         <v>-1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A7" si="0">"LSF_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>LSF_002</v>
+      </c>
+      <c r="B3" s="4">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="C3" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>LSF_003</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>LSF_004</v>
+      </c>
+      <c r="B5" s="4">
         <v>59999</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="C5" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>LSF_005</v>
+      </c>
+      <c r="B6" s="4">
         <v>60000</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="C6" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>LSF_006</v>
+      </c>
+      <c r="B7" s="4">
         <v>60001</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2778,66 +3189,93 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>"RSF_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>RSF_001</v>
+      </c>
+      <c r="B2" s="4">
         <v>-1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A7" si="0">"RSF_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>RSF_002</v>
+      </c>
+      <c r="B3" s="4">
         <v>0</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="C3" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>RSF_003</v>
+      </c>
+      <c r="B4" s="4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>RSF_004</v>
+      </c>
+      <c r="B5" s="4">
         <v>99</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
+      <c r="C5" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>RSF_005</v>
+      </c>
+      <c r="B6" s="4">
         <v>100</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="4">
+      <c r="C6" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>RSF_006</v>
+      </c>
+      <c r="B7" s="4">
         <v>101</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2849,124 +3287,144 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="29.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="str">
+        <f>"CW_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>CW_001</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="str">
+        <f t="shared" ref="A3:A5" si="0">"CW_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>CW_002</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CW_003</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>CW_004</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="10"/>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
+      <c r="E19" s="10"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
+      <c r="E20" s="10"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
       <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
+      <c r="E22" s="10"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
       <c r="D23" s="10"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
+      <c r="E23" s="10"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="10"/>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
+      <c r="E24" s="10"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="10"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2976,32 +3434,36 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>1</v>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="str">
+        <f>"VRX_"&amp;TEXT(ROW(A1),"000")</f>
+        <v>VRX_001</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>1</v>
@@ -3012,41 +3474,53 @@
       <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>1</v>
+      <c r="E2" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <f t="shared" ref="A3:A9" si="0">"VRX_"&amp;TEXT(ROW(A2),"000")</f>
+        <v>VRX_002</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>1</v>
+      <c r="E3" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <f t="shared" si="0"/>
+        <v>VRX_003</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>1</v>
-      </c>
       <c r="D4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <f t="shared" si="0"/>
+        <v>VRX_004</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>2</v>
@@ -3054,52 +3528,68 @@
       <c r="D5" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>2</v>
       </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="str">
+        <f t="shared" si="0"/>
+        <v>VRX_005</v>
+      </c>
       <c r="B6" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="str">
+        <f t="shared" si="0"/>
+        <v>VRX_006</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>1</v>
-      </c>
       <c r="C7" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="str">
+        <f t="shared" si="0"/>
+        <v>VRX_007</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>2</v>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="str">
+        <f t="shared" si="0"/>
+        <v>VRX_008</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>2</v>
@@ -3108,6 +3598,9 @@
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>2</v>
       </c>
     </row>

--- a/testcase/testcase.xlsx
+++ b/testcase/testcase.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8040" tabRatio="884"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8040" tabRatio="884" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ControlHeadLight" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="100">
   <si>
     <t>speedRxState</t>
   </si>
@@ -238,6 +238,105 @@
   <si>
     <t>testCaseId</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testCaseId</t>
+  </si>
+  <si>
+    <t>DL_001</t>
+  </si>
+  <si>
+    <t>DOOR_UNLOCKED</t>
+  </si>
+  <si>
+    <t>DL_002</t>
+  </si>
+  <si>
+    <t>DOOR_LOCKED</t>
+  </si>
+  <si>
+    <t>DL_003</t>
+  </si>
+  <si>
+    <t>DL_004</t>
+  </si>
+  <si>
+    <t>DL_005</t>
+  </si>
+  <si>
+    <t>DL_006</t>
+  </si>
+  <si>
+    <t>DL_007</t>
+  </si>
+  <si>
+    <t>DL_008</t>
+  </si>
+  <si>
+    <t>DL_009</t>
+  </si>
+  <si>
+    <t>DL_010</t>
+  </si>
+  <si>
+    <t>DL_011</t>
+  </si>
+  <si>
+    <t>DL_012</t>
+  </si>
+  <si>
+    <t>DL_013</t>
+  </si>
+  <si>
+    <t>DL_014</t>
+  </si>
+  <si>
+    <t>DL_015</t>
+  </si>
+  <si>
+    <t>DL_016</t>
+  </si>
+  <si>
+    <t>DL_017</t>
+  </si>
+  <si>
+    <t>DL_018</t>
+  </si>
+  <si>
+    <t>DL_019</t>
+  </si>
+  <si>
+    <t>DL_020</t>
+  </si>
+  <si>
+    <t>DL_021</t>
+  </si>
+  <si>
+    <t>DL_022</t>
+  </si>
+  <si>
+    <t>DL_023</t>
+  </si>
+  <si>
+    <t>DL_024</t>
+  </si>
+  <si>
+    <t>DL_025</t>
+  </si>
+  <si>
+    <t>DL_026</t>
+  </si>
+  <si>
+    <t>DL_027</t>
+  </si>
+  <si>
+    <t>DL_028</t>
+  </si>
+  <si>
+    <t>DL_029</t>
+  </si>
+  <si>
+    <t>DL_030</t>
   </si>
 </sst>
 </file>
@@ -1817,7 +1916,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>10</v>
@@ -1839,9 +1938,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="str">
-        <f>"DL_"&amp;TEXT(ROW(A1),"000")</f>
-        <v>DL_001</v>
+      <c r="A2" t="s">
+        <v>68</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>2</v>
@@ -1850,16 +1948,15 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="str">
-        <f t="shared" ref="A3:A31" si="0">"DL_"&amp;TEXT(ROW(A2),"000")</f>
-        <v>DL_002</v>
+      <c r="A3" t="s">
+        <v>70</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>2</v>
@@ -1868,16 +1965,15 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_003</v>
+      <c r="A4" t="s">
+        <v>72</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>1</v>
@@ -1890,16 +1986,15 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_004</v>
+      <c r="A5" t="s">
+        <v>73</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>1</v>
@@ -1912,16 +2007,15 @@
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_005</v>
+      <c r="A6" t="s">
+        <v>74</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>1</v>
@@ -1934,16 +2028,15 @@
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_006</v>
+      <c r="A7" t="s">
+        <v>75</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>1</v>
@@ -1956,16 +2049,15 @@
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_007</v>
+      <c r="A8" t="s">
+        <v>76</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>1</v>
@@ -1978,16 +2070,15 @@
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_008</v>
+      <c r="A9" t="s">
+        <v>77</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>1</v>
@@ -2000,16 +2091,15 @@
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_009</v>
+      <c r="A10" t="s">
+        <v>78</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>1</v>
@@ -2022,16 +2112,15 @@
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_010</v>
+      <c r="A11" t="s">
+        <v>79</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>1</v>
@@ -2044,16 +2133,15 @@
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_011</v>
+      <c r="A12" t="s">
+        <v>80</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>1</v>
@@ -2066,16 +2154,15 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_012</v>
+      <c r="A13" t="s">
+        <v>81</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>1</v>
@@ -2088,16 +2175,15 @@
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_013</v>
+      <c r="A14" t="s">
+        <v>82</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>1</v>
@@ -2112,16 +2198,15 @@
         <v>14</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_014</v>
+      <c r="A15" t="s">
+        <v>83</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>1</v>
@@ -2136,16 +2221,15 @@
         <v>14</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_015</v>
+      <c r="A16" t="s">
+        <v>84</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>1</v>
@@ -2160,16 +2244,15 @@
         <v>15</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_016</v>
+      <c r="A17" t="s">
+        <v>85</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>1</v>
@@ -2184,16 +2267,15 @@
         <v>15</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_017</v>
+      <c r="A18" t="s">
+        <v>86</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>1</v>
@@ -2208,16 +2290,15 @@
         <v>16</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_018</v>
+      <c r="A19" t="s">
+        <v>87</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>1</v>
@@ -2232,16 +2313,15 @@
         <v>16</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_019</v>
+      <c r="A20" t="s">
+        <v>88</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>1</v>
@@ -2256,16 +2336,15 @@
         <v>14</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_020</v>
+      <c r="A21" t="s">
+        <v>89</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>1</v>
@@ -2280,16 +2359,15 @@
         <v>14</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_021</v>
+      <c r="A22" t="s">
+        <v>90</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>1</v>
@@ -2304,16 +2382,15 @@
         <v>15</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_022</v>
+      <c r="A23" t="s">
+        <v>91</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>1</v>
@@ -2328,16 +2405,15 @@
         <v>15</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_023</v>
+      <c r="A24" t="s">
+        <v>92</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>1</v>
@@ -2352,16 +2428,15 @@
         <v>16</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_024</v>
+      <c r="A25" t="s">
+        <v>93</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>1</v>
@@ -2376,16 +2451,15 @@
         <v>16</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_025</v>
+      <c r="A26" t="s">
+        <v>94</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>1</v>
@@ -2400,16 +2474,15 @@
         <v>14</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_026</v>
+      <c r="A27" t="s">
+        <v>95</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>1</v>
@@ -2424,16 +2497,15 @@
         <v>14</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_027</v>
+      <c r="A28" t="s">
+        <v>96</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>1</v>
@@ -2448,16 +2520,15 @@
         <v>15</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_028</v>
+      <c r="A29" t="s">
+        <v>97</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>1</v>
@@ -2472,16 +2543,15 @@
         <v>15</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_029</v>
+      <c r="A30" t="s">
+        <v>98</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>1</v>
@@ -2496,16 +2566,15 @@
         <v>16</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="str">
-        <f t="shared" si="0"/>
-        <v>DL_030</v>
+      <c r="A31" t="s">
+        <v>99</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>1</v>
@@ -2520,10 +2589,10 @@
         <v>16</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>12</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
